--- a/Procesamiento de datos/Output/tabla_entropy_balance.xlsx
+++ b/Procesamiento de datos/Output/tabla_entropy_balance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/florenciaruiz/Library/Mobile Documents/com~apple~CloudDocs/RA Maria/Tres de Febrero/Procesamiento de datos/Output/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/florenciaruiz/Library/Mobile Documents/com~apple~CloudDocs/RA Maria/Tres de Febrero/Tres_de_Febrero/Procesamiento de datos/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71B1BC0-297E-1C49-BB8A-92F90BBA33EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C274FD-42A7-C54A-8FD3-E4EBA3F10A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>variable</t>
   </si>
@@ -99,6 +99,18 @@
   </si>
   <si>
     <t>smdcontrol14</t>
+  </si>
+  <si>
+    <t>mean_1control23</t>
+  </si>
+  <si>
+    <t>mean_0control23</t>
+  </si>
+  <si>
+    <t>diffcontrol23</t>
+  </si>
+  <si>
+    <t>smdcontrol23</t>
   </si>
   <si>
     <t>mean_1control29</t>
@@ -522,13 +534,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -580,856 +592,1060 @@
       <c r="Q1" t="s">
         <v>33</v>
       </c>
+      <c r="R1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S1" t="s">
+        <v>35</v>
+      </c>
+      <c r="T1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>48.166666666666657</v>
+        <v>47.5</v>
       </c>
       <c r="C2" s="1">
-        <v>50.153846740722656</v>
+        <v>48.166667938232422</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.9871795177459717</v>
+        <v>-0.66666668653488159</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.28097197413444519</v>
+        <v>-9.7817346453666687E-2</v>
       </c>
       <c r="F2" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>51.833332061767578</v>
+      </c>
+      <c r="H2" s="1">
+        <v>-4.3333334922790527</v>
+      </c>
+      <c r="I2" s="1">
+        <v>-0.63174569606781006</v>
+      </c>
+      <c r="J2" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="K2" s="1">
         <v>46.5</v>
       </c>
-      <c r="G2" s="1">
-        <v>50.923076629638672</v>
-      </c>
-      <c r="H2" s="1">
-        <v>-4.4230771064758301</v>
-      </c>
-      <c r="I2" s="1">
-        <v>-0.59032917022705078</v>
-      </c>
-      <c r="J2" s="1">
-        <v>46.666666666666657</v>
-      </c>
-      <c r="K2" s="1">
-        <v>50.846153259277344</v>
-      </c>
       <c r="L2" s="1">
-        <v>-4.1794872283935547</v>
+        <v>1</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.58656644821166992</v>
+        <v>0.12749806046485901</v>
       </c>
       <c r="N2" s="1">
-        <v>46.166666666666657</v>
+        <v>47.5</v>
       </c>
       <c r="O2" s="1">
-        <v>51.076923370361328</v>
+        <v>46.666667938232422</v>
       </c>
       <c r="P2" s="1">
-        <v>-4.9102563858032227</v>
+        <v>0.83333331346511841</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.72870492935180664</v>
+        <v>0.11589734256267548</v>
+      </c>
+      <c r="R2" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="S2" s="1">
+        <v>46.166667938232422</v>
+      </c>
+      <c r="T2" s="1">
+        <v>1.3333333730697632</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.1999875009059906</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
+        <v>14.51156532764435</v>
+      </c>
+      <c r="C3" s="1">
         <v>14.87787914276123</v>
       </c>
-      <c r="C3" s="1">
-        <v>13.651653289794922</v>
-      </c>
       <c r="D3" s="1">
-        <v>1.2262256145477295</v>
+        <v>-0.36631381511688232</v>
       </c>
       <c r="E3" s="1">
-        <v>0.22669148445129395</v>
+        <v>-5.3472269326448441E-2</v>
       </c>
       <c r="F3" s="1">
-        <v>12.8508814573288</v>
+        <v>14.51156532764435</v>
       </c>
       <c r="G3" s="1">
-        <v>14.587190628051758</v>
+        <v>13.93410587310791</v>
       </c>
       <c r="H3" s="1">
-        <v>-1.7363095283508301</v>
+        <v>0.57745963335037231</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.25202184915542603</v>
+        <v>7.0536777377128601E-2</v>
       </c>
       <c r="J3" s="1">
-        <v>12.18309263388316</v>
+        <v>14.51156532764435</v>
       </c>
       <c r="K3" s="1">
-        <v>14.895401000976562</v>
+        <v>12.850881576538086</v>
       </c>
       <c r="L3" s="1">
-        <v>-2.7123086452484131</v>
+        <v>1.6606838703155518</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.41075849533081055</v>
+        <v>0.18733680248260498</v>
       </c>
       <c r="N3" s="1">
-        <v>15.43184872468313</v>
+        <v>14.51156532764435</v>
       </c>
       <c r="O3" s="1">
-        <v>13.395975112915039</v>
+        <v>12.183093070983887</v>
       </c>
       <c r="P3" s="1">
-        <v>2.0358734130859375</v>
+        <v>2.3284726142883301</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.31512671709060669</v>
+        <v>0.27209383249282837</v>
+      </c>
+      <c r="R3" s="1">
+        <v>14.51156532764435</v>
+      </c>
+      <c r="S3" s="1">
+        <v>15.431848526000977</v>
+      </c>
+      <c r="T3" s="1">
+        <v>-0.92028337717056274</v>
+      </c>
+      <c r="U3" s="1">
+        <v>-0.1107124462723732</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>41.833333333333343</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1">
-        <v>47.615383148193359</v>
+        <v>41.833332061767578</v>
       </c>
       <c r="D4" s="1">
-        <v>-5.7820510864257812</v>
+        <v>-1.8333333730697632</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.44327425956726074</v>
+        <v>-0.17833565175533295</v>
       </c>
       <c r="F4" s="1">
-        <v>52.166666666666657</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1">
-        <v>42.846153259277344</v>
+        <v>55.333332061767578</v>
       </c>
       <c r="H4" s="1">
-        <v>9.3205127716064453</v>
+        <v>-15.333333015441895</v>
       </c>
       <c r="I4" s="1">
-        <v>0.56824243068695068</v>
+        <v>-1.0196573734283447</v>
       </c>
       <c r="J4" s="1">
+        <v>40</v>
+      </c>
+      <c r="K4" s="1">
+        <v>52.166667938232422</v>
+      </c>
+      <c r="L4" s="1">
+        <v>-12.166666984558105</v>
+      </c>
+      <c r="M4" s="1">
+        <v>-0.71336567401885986</v>
+      </c>
+      <c r="N4" s="1">
+        <v>40</v>
+      </c>
+      <c r="O4" s="1">
         <v>41</v>
       </c>
-      <c r="K4" s="1">
-        <v>48</v>
-      </c>
-      <c r="L4" s="1">
-        <v>-7</v>
-      </c>
-      <c r="M4" s="1">
-        <v>-0.53322857618331909</v>
-      </c>
-      <c r="N4" s="1">
-        <v>44.666666666666657</v>
-      </c>
-      <c r="O4" s="1">
-        <v>46.307693481445312</v>
-      </c>
       <c r="P4" s="1">
-        <v>-1.6410256624221802</v>
+        <v>-1</v>
       </c>
       <c r="Q4" s="1">
-        <v>-0.1212257519364357</v>
+        <v>-9.3658581376075745E-2</v>
+      </c>
+      <c r="R4" s="1">
+        <v>40</v>
+      </c>
+      <c r="S4" s="1">
+        <v>44.666667938232422</v>
+      </c>
+      <c r="T4" s="1">
+        <v>-4.6666665077209473</v>
+      </c>
+      <c r="U4" s="1">
+        <v>-0.42755317687988281</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>72.9623260591692</v>
+        <v>68.098096153846157</v>
       </c>
       <c r="C5" s="1">
-        <v>75.451126098632812</v>
+        <v>72.962326049804688</v>
       </c>
       <c r="D5" s="1">
-        <v>-2.4887974262237549</v>
+        <v>-4.864229679107666</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.22413255274295807</v>
+        <v>-0.39348182082176208</v>
       </c>
       <c r="F5" s="1">
-        <v>69.882788986788981</v>
+        <v>68.098096153846157</v>
       </c>
       <c r="G5" s="1">
-        <v>76.872451782226562</v>
+        <v>76.304779052734375</v>
       </c>
       <c r="H5" s="1">
-        <v>-6.989659309387207</v>
+        <v>-8.2066850662231445</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.71366733312606812</v>
+        <v>-0.70276719331741333</v>
       </c>
       <c r="J5" s="1">
-        <v>69.562836605836608</v>
+        <v>68.098096153846157</v>
       </c>
       <c r="K5" s="1">
-        <v>77.020118713378906</v>
+        <v>69.882789611816406</v>
       </c>
       <c r="L5" s="1">
-        <v>-7.4572820663452148</v>
+        <v>-1.7846928834915161</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.7684551477432251</v>
+        <v>-0.16402119398117065</v>
       </c>
       <c r="N5" s="1">
-        <v>68.190503272503278</v>
+        <v>68.098096153846157</v>
       </c>
       <c r="O5" s="1">
-        <v>77.65350341796875</v>
+        <v>69.562835693359375</v>
       </c>
       <c r="P5" s="1">
-        <v>-9.4630002975463867</v>
+        <v>-1.4647403955459595</v>
       </c>
       <c r="Q5" s="1">
-        <v>-1.0411660671234131</v>
+        <v>-0.13519920408725739</v>
+      </c>
+      <c r="R5" s="1">
+        <v>68.098096153846157</v>
+      </c>
+      <c r="S5" s="1">
+        <v>68.190505981445312</v>
+      </c>
+      <c r="T5" s="1">
+        <v>-9.2407122254371643E-2</v>
+      </c>
+      <c r="U5" s="1">
+        <v>-8.912552148103714E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>3.666666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="C6" s="1">
-        <v>3.461538553237915</v>
+        <v>3.6666667461395264</v>
       </c>
       <c r="D6" s="1">
-        <v>0.20512820780277252</v>
+        <v>-0.4166666567325592</v>
       </c>
       <c r="E6" s="1">
-        <v>0.26453688740730286</v>
+        <v>-0.54168921709060669</v>
       </c>
       <c r="F6" s="1">
-        <v>3.166666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="G6" s="1">
-        <v>3.692307710647583</v>
+        <v>3.3333332538604736</v>
       </c>
       <c r="H6" s="1">
-        <v>-0.52564102411270142</v>
+        <v>-8.3333335816860199E-2</v>
       </c>
       <c r="I6" s="1">
-        <v>-0.55968326330184937</v>
+        <v>-7.6338104903697968E-2</v>
       </c>
       <c r="J6" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="K6" s="1">
+        <v>3.1666667461395264</v>
+      </c>
+      <c r="L6" s="1">
+        <v>8.3333335816860199E-2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>7.7991828322410583E-2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="O6" s="1">
         <v>3</v>
       </c>
-      <c r="K6" s="1">
-        <v>3.769230842590332</v>
-      </c>
-      <c r="L6" s="1">
-        <v>-0.76923078298568726</v>
-      </c>
-      <c r="M6" s="1">
-        <v>-0.87126880884170532</v>
-      </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.24301259219646454</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="S6" s="1">
         <v>3.5</v>
       </c>
-      <c r="O6" s="1">
-        <v>3.538461446762085</v>
-      </c>
-      <c r="P6" s="1">
-        <v>-3.8461539894342422E-2</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>-4.8927206546068192E-2</v>
+      <c r="T6" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="U6" s="1">
+        <v>-0.32053038477897644</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>3.666666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="C7" s="1">
-        <v>3.461538553237915</v>
+        <v>3.6666667461395264</v>
       </c>
       <c r="D7" s="1">
-        <v>0.20512820780277252</v>
+        <v>-0.4166666567325592</v>
       </c>
       <c r="E7" s="1">
-        <v>0.26453688740730286</v>
+        <v>-0.54168921709060669</v>
       </c>
       <c r="F7" s="1">
-        <v>3.166666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="G7" s="1">
-        <v>3.692307710647583</v>
+        <v>3.3333332538604736</v>
       </c>
       <c r="H7" s="1">
-        <v>-0.52564102411270142</v>
+        <v>-8.3333335816860199E-2</v>
       </c>
       <c r="I7" s="1">
-        <v>-0.55968326330184937</v>
+        <v>-7.6338104903697968E-2</v>
       </c>
       <c r="J7" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="K7" s="1">
+        <v>3.1666667461395264</v>
+      </c>
+      <c r="L7" s="1">
+        <v>8.3333335816860199E-2</v>
+      </c>
+      <c r="M7" s="1">
+        <v>7.7991828322410583E-2</v>
+      </c>
+      <c r="N7" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="O7" s="1">
         <v>3</v>
       </c>
-      <c r="K7" s="1">
-        <v>3.769230842590332</v>
-      </c>
-      <c r="L7" s="1">
-        <v>-0.76923078298568726</v>
-      </c>
-      <c r="M7" s="1">
-        <v>-0.87126880884170532</v>
-      </c>
-      <c r="N7" s="1">
+      <c r="P7" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0.24301259219646454</v>
+      </c>
+      <c r="R7" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="S7" s="1">
         <v>3.5</v>
       </c>
-      <c r="O7" s="1">
-        <v>3.538461446762085</v>
-      </c>
-      <c r="P7" s="1">
-        <v>-3.8461539894342422E-2</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>-4.8927206546068192E-2</v>
+      <c r="T7" s="1">
+        <v>-0.25</v>
+      </c>
+      <c r="U7" s="1">
+        <v>-0.32053038477897644</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>43.746419906616211</v>
+        <v>44.781267166137702</v>
       </c>
       <c r="C8" s="1">
-        <v>42.516548156738281</v>
+        <v>43.746421813964844</v>
       </c>
       <c r="D8" s="1">
-        <v>1.2298711538314819</v>
+        <v>1.0348472595214844</v>
       </c>
       <c r="E8" s="1">
-        <v>0.20680539309978485</v>
+        <v>0.19137425720691681</v>
       </c>
       <c r="F8" s="1">
-        <v>41.332894007364906</v>
+        <v>44.781267166137702</v>
       </c>
       <c r="G8" s="1">
-        <v>43.630485534667969</v>
+        <v>42.839630126953125</v>
       </c>
       <c r="H8" s="1">
-        <v>-2.2975897789001465</v>
+        <v>1.9416389465332031</v>
       </c>
       <c r="I8" s="1">
-        <v>-0.3026958703994751</v>
+        <v>0.26517513394355774</v>
       </c>
       <c r="J8" s="1">
-        <v>39.943995157877602</v>
+        <v>44.781267166137702</v>
       </c>
       <c r="K8" s="1">
-        <v>44.271514892578125</v>
+        <v>41.332893371582031</v>
       </c>
       <c r="L8" s="1">
-        <v>-4.3275189399719238</v>
+        <v>3.4483730792999268</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.62190407514572144</v>
+        <v>0.41669651865959167</v>
       </c>
       <c r="N8" s="1">
-        <v>43.749965031941727</v>
+        <v>44.781267166137702</v>
       </c>
       <c r="O8" s="1">
-        <v>42.514911651611328</v>
+        <v>39.943996429443359</v>
       </c>
       <c r="P8" s="1">
-        <v>1.2350524663925171</v>
+        <v>4.8372721672058105</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.17427971959114075</v>
+        <v>0.64259397983551025</v>
+      </c>
+      <c r="R8" s="1">
+        <v>44.781267166137702</v>
+      </c>
+      <c r="S8" s="1">
+        <v>43.749965667724609</v>
+      </c>
+      <c r="T8" s="1">
+        <v>1.0313020944595337</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.13943259418010712</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>0.39333333333333348</v>
+        <v>0.46250000000000002</v>
       </c>
       <c r="C9" s="1">
-        <v>0.39307692646980286</v>
+        <v>0.39333334565162659</v>
       </c>
       <c r="D9" s="1">
-        <v>2.5641024694778025E-4</v>
+        <v>6.9166667759418488E-2</v>
       </c>
       <c r="E9" s="1">
-        <v>1.5119218733161688E-3</v>
+        <v>0.29052606225013733</v>
       </c>
       <c r="F9" s="1">
-        <v>0.36999999999999988</v>
+        <v>0.46250000000000002</v>
       </c>
       <c r="G9" s="1">
-        <v>0.4038461446762085</v>
+        <v>0.33833333849906921</v>
       </c>
       <c r="H9" s="1">
-        <v>-3.3846154808998108E-2</v>
+        <v>0.12416666746139526</v>
       </c>
       <c r="I9" s="1">
-        <v>-0.21321995556354523</v>
+        <v>0.54845428466796875</v>
       </c>
       <c r="J9" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.46250000000000002</v>
       </c>
       <c r="K9" s="1">
-        <v>0.38230767846107483</v>
+        <v>0.37000000476837158</v>
       </c>
       <c r="L9" s="1">
-        <v>3.4358974546194077E-2</v>
+        <v>9.2500001192092896E-2</v>
       </c>
       <c r="M9" s="1">
-        <v>0.21451488137245178</v>
+        <v>0.4099755585193634</v>
       </c>
       <c r="N9" s="1">
-        <v>0.38833333333333342</v>
+        <v>0.46250000000000002</v>
       </c>
       <c r="O9" s="1">
-        <v>0.39538460969924927</v>
+        <v>0.4166666567325592</v>
       </c>
       <c r="P9" s="1">
-        <v>-7.0512820966541767E-3</v>
+        <v>4.583333432674408E-2</v>
       </c>
       <c r="Q9" s="1">
-        <v>-4.2456451803445816E-2</v>
+        <v>0.20157639682292938</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0.46250000000000002</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.38833332061767578</v>
+      </c>
+      <c r="T9" s="1">
+        <v>7.4166662991046906E-2</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0.31718868017196655</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>33.433783531188958</v>
+        <v>31.75</v>
       </c>
       <c r="C10" s="1">
-        <v>29.229305267333984</v>
+        <v>33.433784484863281</v>
       </c>
       <c r="D10" s="1">
-        <v>4.2044787406921387</v>
+        <v>-1.6837835311889648</v>
       </c>
       <c r="E10" s="1">
-        <v>0.58132702112197876</v>
+        <v>-0.70296883583068848</v>
       </c>
       <c r="F10" s="1">
-        <v>26.40214471817017</v>
+        <v>31.75</v>
       </c>
       <c r="G10" s="1">
-        <v>32.2572021484375</v>
+        <v>22.984367370605469</v>
       </c>
       <c r="H10" s="1">
-        <v>-5.8550577163696289</v>
+        <v>8.7656335830688477</v>
       </c>
       <c r="I10" s="1">
-        <v>-0.55270397663116455</v>
+        <v>0.98583024740219116</v>
       </c>
       <c r="J10" s="1">
-        <v>34.184080123901367</v>
+        <v>31.75</v>
       </c>
       <c r="K10" s="1">
-        <v>29.264150619506836</v>
+        <v>26.402145385742188</v>
       </c>
       <c r="L10" s="1">
-        <v>4.9199295043945312</v>
+        <v>5.3478550910949707</v>
       </c>
       <c r="M10" s="1">
-        <v>0.70166397094726562</v>
+        <v>0.52425271272659302</v>
       </c>
       <c r="N10" s="1">
-        <v>32.497282028198242</v>
+        <v>31.75</v>
       </c>
       <c r="O10" s="1">
-        <v>29.697555541992188</v>
+        <v>34.18408203125</v>
       </c>
       <c r="P10" s="1">
-        <v>2.7997264862060547</v>
+        <v>-2.4340801239013672</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.36517259478569031</v>
+        <v>-0.9071347713470459</v>
+      </c>
+      <c r="R10" s="1">
+        <v>31.75</v>
+      </c>
+      <c r="S10" s="1">
+        <v>32.497283935546875</v>
+      </c>
+      <c r="T10" s="1">
+        <v>-0.74728202819824219</v>
+      </c>
+      <c r="U10" s="1">
+        <v>-0.1974700391292572</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>33.476414044698082</v>
+        <v>31.75</v>
       </c>
       <c r="C11" s="1">
-        <v>29.401451110839844</v>
+        <v>33.476413726806641</v>
       </c>
       <c r="D11" s="1">
-        <v>4.0749630928039551</v>
+        <v>-1.7264140844345093</v>
       </c>
       <c r="E11" s="1">
-        <v>0.53475230932235718</v>
+        <v>-0.5184897780418396</v>
       </c>
       <c r="F11" s="1">
+        <v>31.75</v>
+      </c>
+      <c r="G11" s="1">
+        <v>23.164461135864258</v>
+      </c>
+      <c r="H11" s="1">
+        <v>8.5855388641357422</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.9551047682762146</v>
+      </c>
+      <c r="J11" s="1">
+        <v>31.75</v>
+      </c>
+      <c r="K11" s="1">
         <v>27.331794738769531</v>
       </c>
-      <c r="G11" s="1">
-        <v>32.078224182128906</v>
-      </c>
-      <c r="H11" s="1">
-        <v>-4.7464303970336914</v>
-      </c>
-      <c r="I11" s="1">
-        <v>-0.43512517213821411</v>
-      </c>
-      <c r="J11" s="1">
-        <v>33.719564437866211</v>
-      </c>
-      <c r="K11" s="1">
-        <v>29.621391296386719</v>
-      </c>
       <c r="L11" s="1">
-        <v>4.0981740951538086</v>
+        <v>4.4182052612304688</v>
       </c>
       <c r="M11" s="1">
-        <v>0.54224973917007446</v>
+        <v>0.4253028929233551</v>
       </c>
       <c r="N11" s="1">
-        <v>32.43100961049398</v>
+        <v>31.75</v>
       </c>
       <c r="O11" s="1">
-        <v>29.924152374267578</v>
+        <v>33.719566345214844</v>
       </c>
       <c r="P11" s="1">
-        <v>2.5068562030792236</v>
+        <v>-1.9695644378662109</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.31669247150421143</v>
+        <v>-0.52980566024780273</v>
+      </c>
+      <c r="R11" s="1">
+        <v>31.75</v>
+      </c>
+      <c r="S11" s="1">
+        <v>32.431011199951172</v>
+      </c>
+      <c r="T11" s="1">
+        <v>-0.68100959062576294</v>
+      </c>
+      <c r="U11" s="1">
+        <v>-0.16992296278476715</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>30.574373245239261</v>
+        <v>31.986111164093021</v>
       </c>
       <c r="C12" s="1">
-        <v>27.972808837890625</v>
+        <v>30.574373245239258</v>
       </c>
       <c r="D12" s="1">
-        <v>2.6015639305114746</v>
+        <v>1.4117379188537598</v>
       </c>
       <c r="E12" s="1">
-        <v>0.39696183800697327</v>
+        <v>0.48378205299377441</v>
       </c>
       <c r="F12" s="1">
-        <v>25.468173027038571</v>
+        <v>31.986111164093021</v>
       </c>
       <c r="G12" s="1">
-        <v>30.329517364501953</v>
+        <v>23.089256286621094</v>
       </c>
       <c r="H12" s="1">
-        <v>-4.8613443374633789</v>
+        <v>8.896855354309082</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.56797915697097778</v>
+        <v>1.1439130306243896</v>
       </c>
       <c r="J12" s="1">
-        <v>30.75982443491618</v>
+        <v>31.986111164093021</v>
       </c>
       <c r="K12" s="1">
-        <v>27.887216567993164</v>
+        <v>25.468172073364258</v>
       </c>
       <c r="L12" s="1">
-        <v>2.872607946395874</v>
+        <v>6.5179381370544434</v>
       </c>
       <c r="M12" s="1">
-        <v>0.4561181366443634</v>
+        <v>0.80588942766189575</v>
       </c>
       <c r="N12" s="1">
-        <v>29.747386614481609</v>
+        <v>31.986111164093021</v>
       </c>
       <c r="O12" s="1">
-        <v>28.354496002197266</v>
+        <v>30.759824752807617</v>
       </c>
       <c r="P12" s="1">
-        <v>1.3928910493850708</v>
+        <v>1.226286768913269</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.2158064991235733</v>
+        <v>0.67339402437210083</v>
+      </c>
+      <c r="R12" s="1">
+        <v>31.986111164093021</v>
+      </c>
+      <c r="S12" s="1">
+        <v>29.747386932373047</v>
+      </c>
+      <c r="T12" s="1">
+        <v>2.2387244701385498</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1.0129449367523193</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>32.428349812825523</v>
+        <v>31.81640625</v>
       </c>
       <c r="C13" s="1">
-        <v>29.051345825195312</v>
+        <v>32.428348541259766</v>
       </c>
       <c r="D13" s="1">
-        <v>3.3770041465759277</v>
+        <v>-0.61194354295730591</v>
       </c>
       <c r="E13" s="1">
-        <v>0.50002175569534302</v>
+        <v>-0.24477569758892059</v>
       </c>
       <c r="F13" s="1">
-        <v>27.031193812688191</v>
+        <v>31.81640625</v>
       </c>
       <c r="G13" s="1">
-        <v>31.542341232299805</v>
+        <v>23.979249954223633</v>
       </c>
       <c r="H13" s="1">
-        <v>-4.5111470222473145</v>
+        <v>7.8371572494506836</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.48513051867485046</v>
+        <v>0.97104156017303467</v>
       </c>
       <c r="J13" s="1">
-        <v>32.767394383748368</v>
+        <v>31.81640625</v>
       </c>
       <c r="K13" s="1">
-        <v>28.894863128662109</v>
+        <v>27.031194686889648</v>
       </c>
       <c r="L13" s="1">
-        <v>3.8725306987762451</v>
+        <v>4.785212516784668</v>
       </c>
       <c r="M13" s="1">
-        <v>0.58299046754837036</v>
+        <v>0.53867977857589722</v>
       </c>
       <c r="N13" s="1">
+        <v>31.81640625</v>
+      </c>
+      <c r="O13" s="1">
+        <v>32.76739501953125</v>
+      </c>
+      <c r="P13" s="1">
+        <v>-0.95098811388015747</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>-0.43633860349655151</v>
+      </c>
+      <c r="R13" s="1">
+        <v>31.81640625</v>
+      </c>
+      <c r="S13" s="1">
         <v>31.652675628662109</v>
       </c>
-      <c r="O13" s="1">
-        <v>29.40934944152832</v>
-      </c>
-      <c r="P13" s="1">
-        <v>2.2433264255523682</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0.32178837060928345</v>
+      <c r="T13" s="1">
+        <v>0.16373062133789062</v>
+      </c>
+      <c r="U13" s="1">
+        <v>5.3108900785446167E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="1">
+        <v>0.35378244519233698</v>
+      </c>
+      <c r="C14" s="1">
         <v>0.2300209254026413</v>
       </c>
-      <c r="C14" s="1">
-        <v>-0.15517833828926086</v>
-      </c>
       <c r="D14" s="1">
-        <v>0.38519924879074097</v>
+        <v>0.12376151978969574</v>
       </c>
       <c r="E14" s="1">
-        <v>0.51291245222091675</v>
+        <v>0.18508459627628326</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.20435815552870429</v>
+        <v>0.35378244519233698</v>
       </c>
       <c r="G14" s="1">
-        <v>4.5304317027330399E-2</v>
+        <v>-0.19898776710033417</v>
       </c>
       <c r="H14" s="1">
-        <v>-0.24966247379779816</v>
+        <v>0.55277019739151001</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.36777359247207642</v>
+        <v>0.77021092176437378</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.20435814559459689</v>
+        <v>0.35378244519233698</v>
       </c>
       <c r="K14" s="1">
-        <v>4.53043133020401E-2</v>
+        <v>-0.20435816049575806</v>
       </c>
       <c r="L14" s="1">
-        <v>-0.24966245889663696</v>
+        <v>0.55814057588577271</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.3473452627658844</v>
+        <v>1.1275478601455688</v>
       </c>
       <c r="N14" s="1">
-        <v>-7.3581183950106294E-2</v>
+        <v>0.35378244519233698</v>
       </c>
       <c r="O14" s="1">
-        <v>-1.5054285526275635E-2</v>
+        <v>-0.20435814559459686</v>
       </c>
       <c r="P14" s="1">
-        <v>-5.8526899665594101E-2</v>
+        <v>0.55814057588577271</v>
       </c>
       <c r="Q14" s="1">
-        <v>-8.3688214421272278E-2</v>
+        <v>0.95623922348022461</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0.35378244519233698</v>
+      </c>
+      <c r="S14" s="1">
+        <v>-7.3581181466579437E-2</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.42736363410949707</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0.81320679187774658</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>71.734839609990786</v>
+        <v>46.350317550147771</v>
       </c>
       <c r="C15" s="1">
-        <v>55.944320678710938</v>
+        <v>71.734840393066406</v>
       </c>
       <c r="D15" s="1">
-        <v>15.790517807006836</v>
+        <v>-25.384521484375</v>
       </c>
       <c r="E15" s="1">
-        <v>0.81510800123214722</v>
+        <v>-1.3502942323684692</v>
       </c>
       <c r="F15" s="1">
-        <v>53.407045340841059</v>
+        <v>46.350317550147771</v>
       </c>
       <c r="G15" s="1">
-        <v>64.403305053710938</v>
+        <v>60.515830993652344</v>
       </c>
       <c r="H15" s="1">
-        <v>-10.996257781982422</v>
+        <v>-14.165512084960938</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.50601553916931152</v>
+        <v>-0.61670726537704468</v>
       </c>
       <c r="J15" s="1">
-        <v>49.639147510182227</v>
+        <v>46.350317550147771</v>
       </c>
       <c r="K15" s="1">
-        <v>66.142333984375</v>
+        <v>53.40704345703125</v>
       </c>
       <c r="L15" s="1">
-        <v>-16.503185272216797</v>
+        <v>-7.0567278861999512</v>
       </c>
       <c r="M15" s="1">
-        <v>-0.79442334175109863</v>
+        <v>-0.32143858075141907</v>
       </c>
       <c r="N15" s="1">
-        <v>58.591883828590177</v>
+        <v>46.350317550147771</v>
       </c>
       <c r="O15" s="1">
-        <v>62.010299682617188</v>
+        <v>49.639148712158203</v>
       </c>
       <c r="P15" s="1">
-        <v>-3.41841721534729</v>
+        <v>-3.288830041885376</v>
       </c>
       <c r="Q15" s="1">
-        <v>-0.17106564342975616</v>
+        <v>-0.15391001105308533</v>
+      </c>
+      <c r="R15" s="1">
+        <v>46.350317550147771</v>
+      </c>
+      <c r="S15" s="1">
+        <v>58.591884613037109</v>
+      </c>
+      <c r="T15" s="1">
+        <v>-12.24156665802002</v>
+      </c>
+      <c r="U15" s="1">
+        <v>-0.67911291122436523</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="C16" s="1">
         <v>2</v>
       </c>
-      <c r="C16" s="1">
-        <v>1.8461538553237915</v>
-      </c>
       <c r="D16" s="1">
-        <v>0.15384615957736969</v>
+        <v>-0.75</v>
       </c>
       <c r="E16" s="1">
-        <v>0.2132411003112793</v>
+        <v>-1.315587043762207</v>
       </c>
       <c r="F16" s="1">
-        <v>1.666666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>1.6666666269302368</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.3333333432674408</v>
+        <v>-0.4166666567325592</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.48795002698898315</v>
+        <v>-0.8197823166847229</v>
       </c>
       <c r="J16" s="1">
-        <v>1.666666666666667</v>
+        <v>1.25</v>
       </c>
       <c r="K16" s="1">
-        <v>2</v>
+        <v>1.6666666269302368</v>
       </c>
       <c r="L16" s="1">
-        <v>-0.3333333432674408</v>
+        <v>-0.4166666567325592</v>
       </c>
       <c r="M16" s="1">
-        <v>-0.48795002698898315</v>
+        <v>-0.8197823166847229</v>
       </c>
       <c r="N16" s="1">
-        <v>1.833333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="O16" s="1">
-        <v>1.923076868057251</v>
+        <v>1.6666666269302368</v>
       </c>
       <c r="P16" s="1">
-        <v>-8.9743591845035553E-2</v>
+        <v>-0.4166666567325592</v>
       </c>
       <c r="Q16" s="1">
-        <v>-0.13302600383758545</v>
+        <v>-0.8197823166847229</v>
+      </c>
+      <c r="R16" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="S16" s="1">
+        <v>1.8333333730697632</v>
+      </c>
+      <c r="T16" s="1">
+        <v>-0.58333331346511841</v>
+      </c>
+      <c r="U16" s="1">
+        <v>-1.2780193090438843</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>52.832611983285773</v>
+        <v>53.224950033012639</v>
       </c>
       <c r="C17" s="1">
-        <v>48.706298828125</v>
+        <v>52.832611083984375</v>
       </c>
       <c r="D17" s="1">
-        <v>4.1263136863708496</v>
+        <v>0.39233803749084473</v>
       </c>
       <c r="E17" s="1">
-        <v>0.4876568615436554</v>
+        <v>5.9718608856201172E-2</v>
       </c>
       <c r="F17" s="1">
-        <v>43.557460240630803</v>
+        <v>53.224950033012639</v>
       </c>
       <c r="G17" s="1">
-        <v>52.987136840820312</v>
+        <v>46.390491485595703</v>
       </c>
       <c r="H17" s="1">
-        <v>-9.4296770095825195</v>
+        <v>6.8344583511352539</v>
       </c>
       <c r="I17" s="1">
-        <v>-1.2242318391799927</v>
+        <v>1.1950081586837769</v>
       </c>
       <c r="J17" s="1">
-        <v>51.041601805489449</v>
+        <v>53.224950033012639</v>
       </c>
       <c r="K17" s="1">
-        <v>49.532917022705078</v>
+        <v>43.557460784912109</v>
       </c>
       <c r="L17" s="1">
-        <v>1.5086835622787476</v>
+        <v>9.6674900054931641</v>
       </c>
       <c r="M17" s="1">
-        <v>0.1477300226688385</v>
+        <v>1.4706591367721558</v>
       </c>
       <c r="N17" s="1">
-        <v>51.903716233350153</v>
+        <v>53.224950033012639</v>
       </c>
       <c r="O17" s="1">
-        <v>49.135021209716797</v>
+        <v>51.041603088378906</v>
       </c>
       <c r="P17" s="1">
-        <v>2.7686970233917236</v>
+        <v>2.1833481788635254</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.27723696827888489</v>
+        <v>0.22413872182369232</v>
+      </c>
+      <c r="R17" s="1">
+        <v>53.224950033012639</v>
+      </c>
+      <c r="S17" s="1">
+        <v>51.903717041015625</v>
+      </c>
+      <c r="T17" s="1">
+        <v>1.3212337493896484</v>
+      </c>
+      <c r="U17" s="1">
+        <v>0.14032372832298279</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1437,53 +1653,65 @@
         <v>0.5</v>
       </c>
       <c r="C18" s="1">
-        <v>0.23076923191547394</v>
+        <v>0.5</v>
       </c>
       <c r="D18" s="1">
-        <v>0.26923078298568726</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>0.5426519513130188</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1">
         <v>0.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.23076923191547394</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="H18" s="1">
-        <v>0.26923078298568726</v>
+        <v>0.1666666716337204</v>
       </c>
       <c r="I18" s="1">
-        <v>0.5426519513130188</v>
+        <v>0.30429032444953918</v>
       </c>
       <c r="J18" s="1">
         <v>0.5</v>
       </c>
       <c r="K18" s="1">
-        <v>0.23076923191547394</v>
+        <v>0.5</v>
       </c>
       <c r="L18" s="1">
-        <v>0.26923078298568726</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1">
-        <v>0.5426519513130188</v>
+        <v>0</v>
       </c>
       <c r="N18" s="1">
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="O18" s="1">
-        <v>0.30769231915473938</v>
+        <v>0.5</v>
       </c>
       <c r="P18" s="1">
-        <v>2.5641025975346565E-2</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="1">
-        <v>5.1414050161838531E-2</v>
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0.3333333432674408</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0.1666666716337204</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0.30429032444953918</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E18 I2:I18 Q2:Q18 M2:M18">
+  <conditionalFormatting sqref="E2:E18 I2:I18 M2:M18 Q2:Q18 U2:U18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>-0.25</formula>
       <formula>0.25</formula>

--- a/Procesamiento de datos/Output/tabla_entropy_balance.xlsx
+++ b/Procesamiento de datos/Output/tabla_entropy_balance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/florenciaruiz/Library/Mobile Documents/com~apple~CloudDocs/RA Maria/Tres de Febrero/Tres_de_Febrero/Procesamiento de datos/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C274FD-42A7-C54A-8FD3-E4EBA3F10A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B70E09-B433-AB4C-8090-153757E9364A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -538,6 +538,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
